--- a/assets/data/study/lantern-shop-workbook.xlsx
+++ b/assets/data/study/lantern-shop-workbook.xlsx
@@ -1228,10 +1228,10 @@
     <t xml:space="preserve">Gift</t>
   </si>
   <si>
-    <t xml:space="preserve">Delivery from</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charge</t>
+    <t xml:space="preserve">Order from</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delivery</t>
   </si>
   <si>
     <t xml:space="preserve">Size from</t>
